--- a/PMI-DZT2/ПМИ ДЗТ/pmi_dzt/dtz1_mode/ДТЗ_1.xlsx
+++ b/PMI-DZT2/ПМИ ДЗТ/pmi_dzt/dtz1_mode/ДТЗ_1.xlsx
@@ -467,122 +467,122 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Side1_tdif</t>
+          <t>TDIF_1_Side1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Side2_tdif</t>
+          <t>TDIF_1_Side2</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Side3_tdif</t>
+          <t>TDIF_1_Side3</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ksch1_tdif</t>
+          <t>TDIF_1_KschemeSide1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ksch2_tdif</t>
+          <t>TDIF_1_KschemeSide2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ksch3_tdif</t>
+          <t>TDIF_1_KschemeSide3</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>comp3i0_rmxu1_tdif</t>
+          <t>TDIF_1_Equaliz3I0s1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>comp3i0_rmxu2_tdif</t>
+          <t>TDIF_1_Equaliz3I0s2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>comp3i0_rmxu3_tdif</t>
+          <t>TDIF_1_Equaliz3I0s3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_EnaDis</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_EnaDis_ctbreak</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_EnaDis</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_EnaDis_ctbreak</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_EnaDis</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_EnaDis_ctbreak</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_EnaDis</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_RstMod</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_EnaDisSelec</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_EnaDis</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_RegBlock</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_RegBlock</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_EnaDis</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rbre1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_RBRE1_EnaDis</t>
         </is>
       </c>
     </row>
@@ -730,257 +730,257 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T1_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_Tbrk</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>T2_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_Tasym</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Inom_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_Inom</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Imin_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_Imin</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ksym_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_Ksym</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LIsym_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_LIsym</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T1_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_Tbrk</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_Tasym</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Inom_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_Inom</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Imin_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_Imin</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ksym_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_Ksym</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>LIsym_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_LIsym</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>T1_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_Tbrk</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>T2_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_Tasym</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Inom_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_Inom</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Imin_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_Imin</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ksym_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_Ksym</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>LIsym_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_LIsym</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Sbaz_tdif</t>
+          <t>TDIF_1_Sbase</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Ubaz_rmxu1_tdif</t>
+          <t>TDIF_1_Unom1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Ubaz_rmxu2_tdif</t>
+          <t>TDIF_1_Unom2</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Ubaz_rmxu3_tdif</t>
+          <t>TDIF_1_Unom3</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Iperv_rmxu1_tdif</t>
+          <t>TDIF_1_IprimSide1</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Iperv_rmxu2_tdif</t>
+          <t>TDIF_1_IprimSide2</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Iperv_rmxu3_tdif</t>
+          <t>TDIF_1_IprimSide3</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Inomterm_rmxu1_tdif</t>
+          <t>TDIF_1_Inomterm1</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Inomterm_rmxu2_tdif</t>
+          <t>TDIF_1_Inomterm2</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Inomterm_rmxu3_tdif</t>
+          <t>TDIF_1_Inomterm3</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Ivtor_rmxu1_tdif</t>
+          <t>TDIF_1_IsecSide1</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Ivtor_rmxu2_tdif</t>
+          <t>TDIF_1_IsecSide2</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Ivtor_rmxu3_tdif</t>
+          <t>TDIF_1_IsecSide3</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Nsch_rmxu1_tdif</t>
+          <t>TDIF_1_ConnGr1</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Nsch_rmxu2_tdif</t>
+          <t>TDIF_1_ConnGr2</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Nsch_rmxu3_tdif</t>
+          <t>TDIF_1_ConnGr3</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>T1_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Top</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Isr_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Iop</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Isrzagrub_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_IopCSS</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>It1_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Irest1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>It2_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Irest2</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Kt1_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Krest1</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Kt2_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Krest2</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>T1_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_Top</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Iset_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_Iop</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>T1_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Tret</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>T2_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Tblock</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Ratio_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_K2Hdiv1H</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>T1_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Tret</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>T2_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Tblock</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>Ratio_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_K5Hdiv1H</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>T1_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_Top</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>Iset_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_Iop</t>
         </is>
       </c>
     </row>
@@ -1190,72 +1190,72 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VYVOD</t>
+          <t>DI_ControllerDisable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>OV_ctr</t>
+          <t>DI_CTR_UIRZ</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>OVst_rctr1</t>
+          <t>DI_CTR_RCTR1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>OVst_rctr2</t>
+          <t>DI_CTR_RCTR2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>OVst_rctr3</t>
+          <t>DI_CTR_RCTR3</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>OV_tdif</t>
+          <t>DI_TDIF</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>OV_pdif1_tdif</t>
+          <t>DI_RESPDIF</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>NaSign_pdif1_tdif</t>
+          <t>DI_RESPDIF_Sign</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>OV_pdif2_tdif</t>
+          <t>DI_INSPDIF</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NaSign_pdif2_tdif</t>
+          <t>DI_INSPDIF_Sign</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>OV_rctr1_tdif</t>
+          <t>DI_ATDIFRCTR</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>OV_tprmofflvlgc</t>
+          <t>DI_TPRMOFFLVLGC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>OV_ptrc1_tprmofflvlgc</t>
+          <t>DI_TJNTPTRC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>OV_rbre1_tprmofflvlgc</t>
+          <t>DI_JNTRBRE</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -1548,352 +1548,352 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_FuncEnabled</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pusk_obryv_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_StrBrkCF</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>srab_obryv_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_OpBrkCF</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pusk_assym_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_StrAsymCF</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>srab_assym_rctr1_ctr</t>
+          <t>CTR_UIRZ_1_RCTR1_OpAsymCF</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_FuncEnabled</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_FuncOperDisabled</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>pusk_obryv_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_StrBrkCF</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>srab_obryv_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_OpBrkCF</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>pusk_assym_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_StrAsymCF</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>srab_assym_rctr2_ctr</t>
+          <t>CTR_UIRZ_1_RCTR2_OpAsymCF</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_FuncEnabled</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_FuncOperDisabled</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>pusk_obryv_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_StrBrkCF</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>srab_obryv_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_OpBrkCF</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>pusk_assym_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_StrAsymCF</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>srab_assym_rctr3_ctr</t>
+          <t>CTR_UIRZ_1_RCTR3_OpAsymCF</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>srab_ctr</t>
+          <t>CTR_UIRZ_1_CTR_UIRZ_CurCircFlt</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>vvod_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_FuncEnabled</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_FuncOperDisabled</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>pusk_A_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_StrPhA</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>srab_A_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhA</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_A_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhAOnSignal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>io_A_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_DE_IA</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>pusk_B_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_StrPhB</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>srab_B_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhB</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_B_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhBOnSignal</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>io_B_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_DE_IB</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>pusk_C_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_StrPhC</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>srab_C_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhC</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_C_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpPhCOnSignal</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>io_C_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_DE_IC</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>pusk_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_Str</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_OpOnSignal</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>srab_pdif2_tdif</t>
+          <t>TDIF_1_PDIF2_Op</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>vvod_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_FuncEnabled</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>pusk_A_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_StrPhA</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>srab_A_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhA</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_A_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhAOnSignal</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>io_A_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_DE_IA</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>pusk_B_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_StrPhB</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>srab_B_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhB</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_B_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhBOnSignal</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>io_B_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_DE_IB</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>pusk_C_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_StrPhC</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>srab_C_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhC</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_C_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpPhCOnSignal</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>io_C_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_DE_IC</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>pusk_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Str</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>srabsign_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_OpOnSignal</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>srab_pdif1_tdif</t>
+          <t>TDIF_1_PDIF1_Op</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>pusk_A_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Str2HIa</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>pusk_B_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Str2HIb</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>pusk_C_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Str2HIc</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>pusk_hf2phar1_tdif</t>
+          <t>TDIF_1_HF2PHAR1_Str2H</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>pusk_A_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Str5HIa</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>pusk_B_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Str5HIb</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>pusk_C_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Str5HIc</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>pusk_hf5phar1_tdif</t>
+          <t>TDIF_1_HF5PHAR1_Str5H</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_FuncEnabled</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>srab_A_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_CurCircAlmPhA</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>srab_B_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_CurCircAlmPhB</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>srab_C_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_CurCircAlmPhC</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>srab_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_CurCircAlm</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>neispr_rctr1_tdif</t>
+          <t>TDIF_1_RCTR1_CurCircFltGen</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>vvod_ptrc1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncEnabled</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_ptrc1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
@@ -1903,27 +1903,27 @@
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>srab_ptrc1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_PTRC1_Op</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rbre1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncEnabled</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rbre1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>zapret_rbre1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_RBRE1_BlkOp</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>pusk_lvalh</t>
+          <t>DZT2_LVALH_1_CALH1_Alarm</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
